--- a/healthcare_surveys/028_skincare_product_layering_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/028_skincare_product_layering_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>Introduction to Skincare Product Layering Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>How Frequently Do You Use Skincare Products?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,44 +561,366 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>How Often Do You Apply Skincare Products In A Day?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skincare_product_layering</t>
+          <t>How Often Do You Layer Different Skincare Products In A Session?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>page_5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Do You Mix And Match Products From Different Brands?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>page_6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Do You Use Multiple Products From The Same Brand?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>page_7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>How Long Have You Been Using Skincare Products?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>page_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What Products Do You Use For Cleansing, Toning, And Moisturizing?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>page_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which Skincare Products Do You Currently Use?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>page_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How Often Do You Find The Products Deliver Satisfactory Results?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How Important Is It To You To Layer Products For Optimal Results?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Which Benefits Do You See When Layering Skincare Products?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>page_13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What Layering Method Do You Prefer?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>page_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How Many Layers Do You Typically Apply At Once?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>page_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What Challenges Do You Face When Layering Skincare Products?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>page_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Do You Experience Any Skin Irritation Or Reactions?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>page_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>What Benefits Do You See When Layering Skincare Products?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>page_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Additional Comments Or Suggestions?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -615,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,34 +965,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>skincare_product_layering_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>skincare_product_layering_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>page_2_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sometimes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>page_2_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>page_2_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>page_8_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>page_9_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>page_12_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>page_13_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>page_13_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>page_14_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>page_15_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>page_15_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
